--- a/英文文章表 -备份.xlsx
+++ b/英文文章表 -备份.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="120">
   <si>
     <t>title</t>
   </si>
@@ -465,6 +465,307 @@
 Hippos have almost no hair.
 Polar bears live in cold places.
 Polar bears eat seals.</t>
+  </si>
+  <si>
+    <t>我/认为/迈克/描述了/这/基本的/外貌/特征/……的/那个/人
+我/尊重/和/敬佩/这/人/……的/拥有/品质/比如/诚实/耐心/自信/和/勇气
+我们/尊重/敬佩/信任/和/支持/那些/人/带有/强大的/自信/和/勇气
+我/认为/我们/可以/提升/我们自己/如果/我们/拥有/积极的/想法/和/强大的/自信
+我/做了/一些/个人的/调查/关于/这些/病人/昨天/然而/我/没有/调查/全部/……的/他们</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许多/青少年/在/这/地理/社团/积极地/练习/技能/解决/问题/和/培养/他们的/能力/在/课堂/项目
+我们/制作/海报/和/准备/演示/书写/日记/和/问候/他人/用/温暖的/和/真诚的/言语
+阅读/杂志/和/表演/在/戏剧/帮助/我们/保持/高的/活力/和/取得/优良的/成绩/在/学校
+我们/只是/实现/我们的/梦想/感受/幸运的/和/庆祝/我们的/成功/带着/一个/愉悦的/心境
+我们/收拾/我们的/行囊/探索/多岩石的/地域/和/参与/在/活动/引导/开阔/我们的/思维
+这/活动/是/真正地/有趣的/和/带给/我们/愉悦/促成/一场/圆满的/庆祝/为/我们的/团队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/踢/球/和/享受/新鲜的/空气/当/雷声/和/闪电/照亮/定冠词/天空/在/下雨的/日子
+当地的/人们/聚集/在/宁静的/地方/和/遵循/古老的/文化/和/传统/快乐地
+这/文章/解释/定冠词/原因/去/延续/我们的/生活/和/保持/活着/穿过/艰难的/时光
+定冠词/接下来的/部分/将要/划分/学生/进入/小组/和/帮助/他们/决定/他们的/自己的/任务
+农民/种植/不同的/农作物/和/保留/他们的/文化/和/传统/作为/部分/属于/当地的/生活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们的/令人惊叹的/星球/拥有/数十亿/属于/自然的/区域/关系代词/覆盖/广阔的/土地/从/严寒的/北极/沙漠/到/高处/关系代词/达到/数/米/高
+一个/小的/颗粒/属于/沙子/一个/巨大的/鲸鱼/和/一只/美丽的/蝴蝶/提供/我们/带有/美好/但是/当/我们/探索/大自然/我们/担忧/一些/活着的/生物/可能/消失/不久
+塑料/污染/和/有害的/化学的/废弃物/污染/地下水/当/人们/燃烧/石油/和/燃气/关系代词/伤害/定冠词/环境/在……周围/我们
+我们/拥有/一个/有用的/网站/关于/沙尘暴/作为/人们/属于/定冠词/新的/一代/我们/应该/展示/我们的/想法/和/寻找/解决办法/去/阻止/沙尘暴/关系代词/刮/强烈地/和/伤害/定冠词/环境
+在/古老的/时代/定冠词/皇帝/带领/人们/去/捕猎/动物/战斗/在/战争/和/保护/他们的/家园/远离/危险的/暴风雨/和/严重的/污染
+我们/必须/行动/去/保护/地下水/停止/燃烧/有害的/石油/和/燃气/减少/塑料/废弃物/和/探索/好的/方式/去/拯救/我们的/广阔的/星球/在……之前/更多/自然的/奇观/消失/不要/浪费/水/和/食物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿着/一套/太空服/我们/准备/为了/太空/冒险/收集/数据/关于/定冠词/宇宙/和/观赏/定冠词/令人惊叹的/表面/属于/其他的/星球/某天
+定冠词/着陆器/能够/通过/低矮的/区域/称重/千克/和/帮助/宇航员/呼吸/轻松地/用/现代的/太空/设备
+科学家/做/实验/留下/老旧的/工具/在后面/旅行/千米/遥远/和/从不/展现/软弱/在/面对/困难
+我们/联结/我们的/勇气/带着/决心/介绍/我们的/太空/项目/发布/新的/发现/和/已经/梦想/关于/极好的/机会
+在/一座/安静的/岛屿/古老的/邻居/聚集/在/一个/圆圈/阅读/优美的/诗歌/表达/他们的/情感/和/传承/古老的/文化/历经/世纪
+定冠词/接下来的/部分/属于/我们的/藏品/解释/为何/我们/继续/我们的/旅行/划分/任务/明智地/和/做出/决定/去/探索/定冠词/世界/更好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个/向导/能够/展示/你/东方/和/西方/在那里/自然的/风景/和/历史的/古迹/融合/与/西方的/风格
+许多/成年人/和/年长的/顾客/游览/热门的/景点/遍及/这个/区域/并且/欣赏/美丽的/艺术品/和/绘画
+我/有/一份/清单/关于/有用的/窍门/和/建议/为了/你/去/欣赏/几乎/每一个/精彩的/景色/和/景观
+这/大门/成为/一种/巨大的/影响/对于/当地的/文化/与此同时/石头/建筑/和/水面/倒影/形成/令人惊叹的/风景
+一位/画家的/妻子/喜欢/记录/每一个/回忆/关于/风景/并且/表达/情感/在/普通的/艺术作品
+什么/其他/能够/我们/设计/去/展示/历史的/文化/我们/能够/创造/新的/风格/并且/变得/受欢迎/受/游客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/欣赏/伟大的/文学/并且/参演/精彩的/活动/并且/每一位/成员/将会/无疑/参加/这场/极好的/年度/活动
+我们/发射/一枚/火箭/带着/巨大的/动力/呼喊/一起/并且/享受/这/难忘的/时刻/作为/一个/团队
+最近/我/参加/一场/慈善/义卖/竞争/公平地/售卖/零食/馅饼/并且/赚取/一些/美元
+我们/远足/在户外/塑造/我们的/身体/使用/必要的/设备/并且/找出/这/差异/在……之间/乐趣/和/困难
+我们/装饰/这/房间/列出/有用的/窍门/设计/一处/优美的/场景/并且/使用/一把/勺子/去/享用/美味的/食物
+总的/来说/这/活动/是/极好的/并且/它/成为/一段/美好的/回忆/对于/每一位/成年人/和/年长的/顾客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的/自己的/收藏/包括/一枚/珍贵的/戒指/一只/柔软的/手套/一枚/硬币/一张/贴纸/和/许多/其他的/可爱的/物品
+我们/拿放/扁平的/物品/小心地/贴上/一张/贴纸/到/一个/信封/并且/开启/真正的/宝藏/用/一根/小的/钉子
+它/似乎/绝对地/不可能/去/解释/一点/丝毫/的/差异/在……之间/两个/相似的/硬币/图案
+我们/制作/一块/糖果/棒/带有/一个/特别的/包装纸/控制/它的/尺寸/并且/这/结果/能够/吸引/许多/小的/昆虫
+人们/浪费/微小的/物品/在/日常的/生活/但是/每一件/物品/是/特别的/并且/能够/成为/一份/巨大的/宝藏/在/我们的/语言
+这件/艺术作品/有/一个/好看的/图案/包含/许多/扁平的/形状/并且/将会/吸引/更多的/游客/去/欣赏/真正的/美好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的/父母/总是/鼓励/我/去/参加/进入/定冠词/竞赛/和/努力/去/实现/我的/未来的/梦想
+他/很少/感到/无聊/因为/他/阅读/在网上/游览/每一个/地点/和/进行/一次/温暖的/淋浴/去/放松
+定冠词/善良的/年老的/男士/将要/退休/不久/并且/定冠词/整个的/社区/评价/高度地/关于/他的/开朗的/和/积极的/性格
+你/应该/使用/你的/智能手机/明智地/注意/到/学习/并且/远离/狭隘的/和/错误的/想法
+我们的/严格的/老师/说/连词/变得/聪明的/和/勤奋的/是/一个/好的/特质/属于/一名/顶尖的/学生
+我的/亲戚/穿着/一件/学校/校服/并且/我们/经常/谈论/关于/这个/话题/在……帮助下/医疗的/工作者/就像/一个/真正的/超人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/计划/去/观光/沿着/定冠词/海岸/并且/我们的/最终的/目的地/是/一家/小的/咖啡馆/带有/一个/完美的/视野/对于/定冠词/火山
+如果/你/想象/一座/巨大的/山脉/你/可以/发现/许多/独特的/植物/和/野生的/动物/像/定冠词/濒危的/狼
+定冠词/政府/保护/自然的/区域/以便/它们/保持/美丽的/并且/森林/延伸/遥远/远离/定冠词/繁忙的/摩托车/道路
+请/写下/你的/家庭/地址/并且/你/将要/收到/一把/钥匙/通往/定冠词/房间/带有/优质的/服务/和/丰盛的/食物
+我们/攀爬/定冠词/楼梯/并且/迈出/一个/小的/脚步/去/提起/我们的/包裹/然后/骑行/一辆/雪地摩托/穿过/宽阔的/田野/去/观看/定冠词/比赛
+人们/大多/饮用/葡萄酒/在/派对/并且/一些/躺/在/草地/去/享受/宁静的/生活/没有/任何/担忧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物/拥有/强壮的/根茎/和/长的/枝干/并且/它们/产生/氧气/去/保护/定冠词/环境
+我们/应该/对待/所有/活着的/物种/友好地/并且/沟通/去/阻止/定冠词/传播/属于/危险
+定冠词/寂静的/森林/能够/俯瞰/定冠词/城市/并且/人类/创造/许多/有用的/事物/从/木材
+这家/商店/售卖/许多/商品/和/家具/并且/它/是/非常/便利的/对于/人们/在/每一个/侧边/属于/定冠词/街道
+不要/挖掘/一个/深的/坑/或者/粘贴/物品/到处/否则/一场/事故/可能/发生/并且/你/可以/借用/工具/如果/你/需要
+学习/知识/帮助/你/理解/每一个/人物/并且/好的/翻译/使/故事/更简单/去/分享</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定冠词/接待员/告诉/定冠词/客人/连词/这家/酒店/不/允许/吸烟/并且/将要/道歉/如果/任何/服务/困扰/他们
+一支/队伍/属于/消防员/和/搜救/工作者/付出/巨大的/努力/去/帮助/人们/在/每一场/灾难
+海豚/和/鲨鱼/生活/在/大海/并且/灰色的/母鸡/产出/蜂蜜相关的/产品/从/它的/特别的/材料
+定冠词/失明的/先生/感到/害怕/当/行走/独自/所以/一名/守卫/将会/运送/他/到/某处/安全的
+我们/可以/或许/看见/动物/像/毛用羊/在/定冠词/源头/属于/定冠词/河流/并且/它们/将要/不/灭绝/随时
+你/可以/游览/定冠词/动物园/某时/去/观看/活着的/物种/并且/要么/研究/它们的/种类/要么/寻找/它们的/生存/规律</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在/这/漫长的/旅途/我们/滴落/水/和/轻敲/管道/并且/最终/我们/返回/去/进行/一次/温暖的/沐浴/用/盐
+我们/应该/调养/我们的/健康/并且/运用/我们的/大脑/良好地/因为/这/是/我们的/责任/去/保持/公共的/场所/干净/和/安全
+农业/和/工业/发挥/一个/重要的/作用/在/一个/国家的/发展/并且/这/人口/影响/它的/商业/和/收入
+人们/交易/不同的/商品/在海外/关系代词/支持/全球的/贸易/并且/创造/机会/为了/几乎/每一个/人
+贯穿/这/一年/许多人/匆忙/为了/工作/而/其他人/享受/闲暇的/时光/并且/形成/丰富多彩的/生活/方式
+我们/养成/好的/习惯/去/服务/公众/并且/我们的/微小的/行为/帮助/提升/整个的/社会/在/许多/方面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阅读/这/说明/在……之前/你/连接/任何/设备/到/电力/为了/你的/安全
+记住/去/关闭/这/电视/设备/和/冰箱/去/节省/电力/和/电池/在/你的/公寓
+这/家庭的/规则/要求/每个人/去/遵守/这/速度/限制/并且/反对/危险的/行为
+你/可以/完成/你的/任务/在/一台/平板/当……时候/你/等待/为了/酸奶/去/变凉/在/冰箱
+一个/适当的/数量/属于/能源/帮助/保护/这/气候/并且/使/我们的/日常的/生活/更轻松
+这/高大的/塔/是/一个/著名的/地标/关系代词/展示/这/城市的/发展/和/现代的/科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许多/受人尊敬的/先驱/在/科技/和/工程/领域/取得/巨大的/成功/并且/获得/这/最高的/奖项
+他们/花费/数年/在/研究/并且/做出/一个/巨大的/贡献/到/教育/和/整个的/社会
+这些/勇敢的/英雄/包括/许多/女性/空降消防员/鼓舞/人们/并且/赢得/公众的/认可/和/赞扬
+我们/敬佩/他们的/坚定的/使命/去/致敬/我们的/国家/并且/他们/找到/新的/方式/去/燃起/希望/为了/其他人
+他们/渴望/去/帮助/并且/保持/规律的/训练/去/保持/健康/适合/艰苦的/工作/在/浓密的/火灾
+他们/使用/实用的/工具/去/扑灭/火灾/关系代词/害死/植物/和/动物/确保/没有人/处于/死亡/或/失踪
+在/某些/危险的/情况/他们/必须/行动/明智地/否则/很少人/能够/幸存/并且/安全/是/他们的/第一/准则
+作为/勇敢的/战士/他们/注入/希望/进入/我们的/内心/并且/我们/感到/自豪/为/每一位/英雄/关系代词/保护/我们的/生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许多/运动员/表演/在/舞台/并且/赢得/欢呼/来自/一大群/观众
+一位/生物学家/表现出/极大的/兴趣/在/大自然/并且/发明/一种/实用的/方法/去/研究/生命
+它/是/可能的/去/提升/你的/能力/凭借/努力/工作/在/你的/一生
+如今/人类/对比/不同的/技能/并且/回顾/他们的/进步/定期地
+她/使用/一种/特殊的/仪器/并且/是/极其/好奇的/关于/这/世界/在……之外/我们的/星球
+他们/航行/穿过/大海/并且/参加/在/一场/比赛/在那里/他们/射击/向/一个/目标/用/一条/皮带
+主持人/进行/一场/生动的/演讲/并且/使/这场/活动/生动/并且/容易/去/理解
+人们/经常/拥抱/和/亲吻/去/表达/善意/并且/事实上/这/是/一种/温暖的/方式/去/交流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>史前的/恐龙/化石/展示/定冠词/诞生/和/死亡/属于/生物/关系代词/生活/完全地/不同的/生活/久远的/以前
+聪慧的/有天赋的/和/有艺术天赋的/艺术家/创作/一件/精彩的/作品/属于/艺术/并且/保留/定冠词/原始的/风格/在/他们的/笔记本
+一位/编辑/帮助/整理/信息/并且/记录/故事/关于/定冠词/整个的/世界/属于/古代的/动物
+或许/一辆/特别的/交通工具/能够/带/我们/回到/去/看/如何/古代的/生物/生活/没有/遭受/苦难
+我们/能够/订购/书籍/关系代词/研究/艺术/和/历史/并且/学习/如何/有创造力的/人们/表达/他们的/想法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/检查/定冠词/航班/时刻表/仔细地/因为/飞机/飞行/到处/并且/时间/事关/精确地
+赢得/定冠词/奖项/是/一个/大的/挑战/但是/我/承诺/去/尽/我的/最大努力/没有/犹豫
+在/定冠词/棋盘/上/银色的/棋子/代表/力量/并且/成为/一个/象征/属于/智慧
+我/想知道/是否/你/将会/回复/并且/同意/去/参加/定冠词/游戏/并且/我们/能够/计分/一起
+目前/大约/九十/百分之/属于/人们/在/这个/省份/遵循/一份/严格的/预算/为了/日常的/生活
+成本/已经/上涨/急剧地/所以/我们/需要/一个/新的/系统/去/管理/金钱/以/良好的/秩序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在/定冠词/数字的/时代/网络/科技/发展/快速地/并且/专家/持续/做出/重大的/突破
+一场/洪水/能够/毁坏/交通/并且/流淌/猛烈地/所以/我们/应该/警告/人们/并且/提供/及时的/救助
+多媒体/工具/展示/信息/在/定冠词/屏幕/属于/一台/笔记本/或/移动/手机/清晰地
+移动/支付/是/基于/数据/和/电子的/软件/运行/平稳地/在/日常的/生活
+许多/公司/开发/实用的/应用程序/关系代词/人们/能够/下载/去/发送/社交的/信息
+在/一场/采访/期间/人们/分享/积极的/和/消极的/观点/并且/留下/评论/关于/一部/小说
+一块/微芯片/和/微处理器/是/微小的/但是/重要的/零件/关系代词/构成/定冠词/基础/属于/数字的/系统
+我们/应该/审视/想法/的/分量/避免/不良的/影响/并且/保持/我们的/网络/生活/健康/和/有序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个/气球/带有/翅膀/能够/飞行/一段/长的/距离/并且/我们/注意/它/几乎/任何地方/在/天空
+轮子/和/金属的/零件/附着/到/定冠词/主体/并且/我们/拉动/它们/沿着/一条/平坦的/路径
+虽然/这项/技术/是/新的/很少/人们/怀疑/它的/用途/并且/它/有益于/国际的/旅行
+发动机/依赖/于/汽油/和/一种/混合物/属于/空气/并且/高的/热量/和/压力/使/它们/运转
+中心的/部件/控制/定冠词/类型/属于/动力/帮助/我们/避免/危险/在/道路/上
+就个人而言/我/相信/这份/陈述/并且/没有/错误的/预测/将会/影响/我们的/安全的/旅程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在/学生/交流/期间/许多人/感到/紧张/和/困惑/在/这种/陌生的/环境
+在/定冠词/旅行/或/蜜月/期间/人们/使用/筷子/学习/太极/并且/应对/外国的/习俗
+一些人/是/思乡的/和/孤独的/然而/他们/努力/去/变得/独立/并且/做出/适应/到/新的/生活
+他们/期待/善意/感到/震撼/对于/文化的/差异/并且/表达/感激的/情感/对/那些/人/关系代词/帮助
+在/这个/特别的/阶段/你/可能/感到/焦虑/起初/但是/你/将会/接受/并且/找到/满足/不久
+人们/互相/帮助/去/适应/并且/不再/感到/陌生/当/面对/文化的/差异</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这位/作者/描写/关于/士兵/和/定冠词/船长/如何/定位/残骸/属于/古老的/营地
+在/午夜/在/浓重的/雾气/中/他们/进入/基地/秘密地/并且/躲避/敌人
+没有人/空手/他们/装满/他们的/背包/并且/前往/定冠词/区域/属于/进攻
+他们/战斗/勇敢地/击败/敌人/并且/成功/在/赢得/一场/伟大的/胜利
+他们/不/开玩笑/或/伪装/他们/不/欺骗/彼此/因此/没有人/将会/失败
+他们/赢得/战争/在/一段/短的/时间/内/除了/一些/受伤/并且/没有/敌人/留存/去/反击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/应该/重复/锻炼/定期地/去/保持/健康的/饮食/并且/维持/精神上/强健
+一些/食物/含有/坚果/和/洋葱/关系代词/尤其/有益/对于/我们的/身体/在/特定的/季节
+当/你/感到/有压力/试着/去/放松/这/能够/关联/到/你/正常的/情绪/并且/避免/体重/下降
+记/笔记/列/清单/并且/使用/视觉的/图像/去/理解/上下文/更好地
+一把/叉子/能够/帮助/你/用餐/整洁地/甚至/一只/小的/蚂蚁/在/大自然/中/给予/我们/一种/强烈的/生命/感
+在/化学/中/我们/做/一份/总结/关于/元素/并且/它们/倾向/于/形成/特殊的/结构/在/大自然/中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一位/忠诚的/仆人/保持/清醒/去/守住/门/并且/保护/女王/免受/任何/袭击
+我们/应该/有责任感/并且/不/乱扔垃圾/在室内/或/室外/因为/这/将会/造成/麻烦/给/其他人
+如果/你/感到/有压力/试着/去/缓解/压力/通过/单纯地/抱怨/不太可能/解决/问题
+居住/在/一套/公寓/是/一种/普遍的/选择/并且/专家/建议/我们/保持/良好的/关系/与/我们的/邻居
+真正的/财富/不是/金钱/而是/一份/温暖的/关系/和/这份/自豪/属于/怀着/善意/生活
+在/这些/故事/当中/那个/魔幻的/故事/讲述/一位/谦卑的/仆人/如何/赢得/尊重/并且/建立/信任/与/女王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许多/志愿者/主动/去/帮助/定冠词/年老的/人和/病人/他们/筹集/资金/和/捐赠/他们的/空闲的/时间/去/对抗/严重的/疾病/像/癌症
+我/想要/去/购买/一些/药品/去/缓解/我的/酸痛/和/疼痛/好的/给/你/阿司匹林/英镑/还是/美元/英镑/谢谢
+低落的/情绪/和/持续的/疼痛/带来/疾病/而/放松/和/愉悦/带来/快乐
+你/正在/失去/你的/理智/乔/你/需要/许可/去/安排/这次/捐赠
+这/平板电脑/属于/你/迈克/你/真是/太/好心/了/吉姆/但是/我/有/一个/严重的/问题/充电器/在/哪里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女士/老板/要求/我们/遵守/我们的/行为/和/表情/在/公共场合
+当/我们/鼓掌/或/点头/它/有/一个/清晰的/含义/并且/留下/一个/好的/印象
+请/提醒/我/去/强调/这些/规则/以防/有人/感到/不舒服
+在/芭蕾/课堂/一个/害羞的/女孩/可能/摇晃/一点/但是/表现/真正地/优美
+如果/你/需要/帮助/告诉/我/直接地/我/将会/立刻/来到/你的/情况
+我/认为/我们/应该/保持/良好的/礼仪/并且/从不/表现/疯狂/在……前面/其他人
+如果/你/有/某物/在/你的/手里/像/拿着/一个/瓶子/和/摇晃/它/你/就/不能/鼓掌
+汤姆/你的/表情/不/清晰/你/是/喝醉的/吗/你/应该/表达/你自己/强烈地/这/留下/一个/更深的/印象/对/其他人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这/主题/属于/这场/表演/是/关于/先进的/人工智能/科技/和/经典的/民间/音乐
+这/主题/属于/这场/表演/结合/先进的/人工智能/科技/和/经典的/民间/音乐
+这/主题/属于/这场/表演/是/关于/结合/先进的/人工智能/科技/和/经典的/民间/音乐
+这/主角/冒着/撞上/进入/定冠词/墙/的/风险/并且/这/墙/倒塌/了
+你/介意/做/一场/演讲/没有/文稿/吗
+一个/警示/提醒/我们/关于/这/风险/属于/缝隙/在/墙/中
+这位/领导/拿着/一片/皮革/和/一根/羽毛/并且/告诉/我们/这些/特征/属于/天气
+我们/推进/我们的/计划/取得/巨大的/进步/并且/获得/一个/优势/胜过/其他人
+我们/跳入/进入/这些/波浪/属于/大海/呼吸/这/咸的/空气/并且/感受/这些/元素/属于/大自然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这位/大师/创作/一件/伟大的/杰作/和/一件/精彩的/雕塑/关系代词/是/无价的
+无论何时/他/感到/孤独/他/专注/于/细节/并且/拒绝/去/模仿/别人的/作品
+这场/展览/想要/保护/这/艺术/并且/避免/损坏/来自/高温
+我们/分隔/不同的/作品/并且/这场/展出/要求/严格的/照料/去/保护/每一个/细节
+他的/女儿/将要/毕业/不久/并且/学习/去/传承/这/特殊的/生活/方式/属于/艺术
+不幸地/时间/可能/限制/保护/但是/我们/仍然/尽/我们的/最大/努力/去/拯救/这些/珍宝
+这位/大师/创作/一件/伟大的/杰作/他/雕刻/一件/无价的/雕塑/但是/不幸地/这/雕塑/被/偷窃/在……期间/这场/展览
+这位/大师的/女儿/模仿/过/这/雕塑/以前/但是/不幸地/高温/已经/损坏/了/这件/仿制品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/能够/辨认/他的/英俊的/脸庞/和/苗条的/身材/从/这/镜子/容易地
+士兵/使用/武力/和/枪支/但是/必须/遵守/法律/并且/从不/惩罚/人们/随意地
+农民/种植/玉米/以/正确的/方向/并且/取得/巨大的/进步/在/农耕/方面
+一位/官员/可能/扔掉/无用的/物品/但是/我们/应该/知道/所有事物/的/真正的/价值
+如果/你/感到/口渴/或/有/喉咙/痛/这/是/典型的/去/感到/担忧/关于/你的/健康
+作家/出版/博客/并且/承载/梦想/在/他们的/肩膀/上/这样的/人才/是/稀少的/在/生活/中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在/舞台/上/美丽的/服装/和/有创意的/诗歌/带来/极大的/愉悦/给/观众
+我们/能够/习得/有用的/技能/并且/提升/我们自己/如果/我们/去/国外/进行/学习
+每一个/小的/线索/帮助/我们/得出/一个/正确的/结论/并且/抓住/这/宝贵的/机会
+在/圣诞/前夕/红润的/笑容/提醒/我们/关于/青春/的/美好/和/热情
+一张/干净的/纸/能够/承载/精彩的/想法/并且/我们/感到/关切/关于/它的/价值
+这样/一次/有意义的/经历/值得/珍惜/和/铭记/在/我们的/一生/中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们/通常/供应/牛肉/和/海鲜/在/餐馆/但是/不是/每个人/能够/负担/得起/它们
+不要/固守/一个/错误/只需/改变/你的/方式/并且/避免/被/撞击/在/健身房
+做/运动/在/健身房/有助于/练就/强壮的/肌肉/并且/保持/你的/身体/处于/良好的/状态
+一颗/卫星/用于/航天/需要/足够的/燃料/和/补给/去/航行/在/太空
+科学家/在/实验室/筛选/数据/并且/计算/平均值/和/可能的/结果
+这些/机器/输送/能源/和/提供/支持/并且/它们/甚至/能够/分解/废弃物/在/太空
+这/要点/属于/该/项目/是/推动/科技/并且/防止/任何事物/被/破坏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不要/提起/这个/故事/今晚/它/将会/使/人们/感到/恐惧
+当/你/咳嗽/并且/你的/喉咙/疼痛/恐惧/可能/使/你/想象/一个/丑陋的/生物
+不要/变得/疯狂/或/拒绝/帮助/在/紧急情况/下
+带上/一台/相机/并且/搭建/一个/帐篷/没有/必要/去/向后/后退
+不要/争论/关于/它/是否/是/真实的/与否/不要/让/它/使/你/失望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>translate-word</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -507,10 +808,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -814,795 +1121,895 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="37.25" customWidth="1"/>
-    <col min="6" max="7" width="7" customWidth="1"/>
+    <col min="1" max="2" width="7" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.25" style="2" customWidth="1"/>
+    <col min="6" max="7" width="7" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+      <c r="H1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
+      <c r="E16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
+      <c r="E19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
+      <c r="E21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
+      <c r="E24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1" t="s">
+      <c r="E25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1" t="s">
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="1" t="s">
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="1" t="s">
+      <c r="E28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="1" t="s">
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="1" t="s">
+      <c r="E30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="1" t="s">
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="1" t="s">
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="1" t="s">
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1">
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
         <v>0</v>
       </c>
     </row>
